--- a/batchstudent/Result/anlpvhe187047/TC4/GradeDetail.xlsx
+++ b/batchstudent/Result/anlpvhe187047/TC4/GradeDetail.xlsx
@@ -158,10 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -170,12 +170,6 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -198,18 +192,6 @@
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -236,7 +218,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -245,17 +227,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -278,7 +250,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -288,14 +260,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -305,14 +271,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -939,11 +897,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R19"/>
+  <x:dimension ref="A1:R12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1050,25 +1008,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1106,7 +1064,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1126,8 +1084,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1147,10 +1105,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1162,7 +1120,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1182,8 +1140,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R4" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1203,13 +1161,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>44</x:v>
@@ -1218,7 +1176,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1238,8 +1196,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R5" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1259,10 +1217,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1274,7 +1232,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1294,8 +1252,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R6" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1315,13 +1273,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>45</x:v>
@@ -1330,7 +1288,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1350,8 +1308,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1371,10 +1329,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1386,7 +1344,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1406,8 +1364,8 @@
       <x:c r="Q8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R8" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1427,10 +1385,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1442,7 +1400,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1462,8 +1420,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R9" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1483,10 +1441,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1498,7 +1456,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1518,8 +1476,8 @@
       <x:c r="Q10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R10" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1539,10 +1497,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1554,7 +1512,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1574,8 +1532,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R11" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1595,10 +1553,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1610,7 +1568,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1630,400 +1588,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:18">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="R13" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:18">
-      <x:c r="A14" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="Q14" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R14" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:18">
-      <x:c r="A15" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M15" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P15" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q15" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="R15" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:18">
-      <x:c r="A16" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L16" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M16" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N16" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P16" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="Q16" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R16" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:18">
-      <x:c r="A17" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M17" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P17" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q17" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="R17" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:18">
-      <x:c r="A18" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M18" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="0">
-        <x:v>60698</x:v>
-      </x:c>
-      <x:c r="Q18" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R18" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:18">
-      <x:c r="A19" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M19" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P19" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q19" s="0">
-        <x:v>60698</x:v>
-      </x:c>
-      <x:c r="R19" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="R12" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
